--- a/Llama-3.1-8B-Instruct_piped_strong_negation_results_processed_results.xlsx
+++ b/Llama-3.1-8B-Instruct_piped_strong_negation_results_processed_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\joshgryzen\logic_grammar\logic_grammar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7350D597-5555-4C8C-8B9A-8EE46C30954E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{931952CA-E621-4333-88E2-93776F262974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
